--- a/Config/Datas/npc_routine.xlsx
+++ b/Config/Datas/npc_routine.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,11 +440,6 @@
           <t>reevaluate_interval_sec</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>relocate_policy</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,11 +462,6 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ENpcRoutineRelocatePolicy</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -494,11 +484,6 @@
           <t>c,s</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -521,11 +506,6 @@
           <t>rule reevaluation interval</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Move or Snap</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -540,11 +520,6 @@
       </c>
       <c r="D5" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Move</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -883,7 +858,6 @@
           <t>vera_wait_report</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -937,7 +911,6 @@
           <t>vera_sleep_area</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>0</v>
       </c>
@@ -991,7 +964,6 @@
           <t>vera_work_area</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>1.5</v>
       </c>
@@ -1045,7 +1017,6 @@
           <t>vera_default</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>0</v>
       </c>

--- a/Config/Datas/npc_routine.xlsx
+++ b/Config/Datas/npc_routine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="npc_routine_profile" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="npc_routine_rule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="npc_routine_binding" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="npc_locomotion_profile" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_routine_profile" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_routine_rule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_routine_binding" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_locomotion_profile" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,6 +520,66 @@
       </c>
       <c r="D5" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>home01_emon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>home01_emon_pre</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>home01_duran</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>home01_duran_pre</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>home01_evan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>home01_evan_pre</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>home01_hearn</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>home01_hearn_pre</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -533,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1038,6 +1098,561 @@
       <c r="N8" t="inlineStr">
         <is>
           <t>vera_default</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>home01_emon_pre</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>home01_emon</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AnchorPoint</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>home_pre_survivor_fire</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>pre</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>home01_emon_pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>home01_emon_post</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>home01_emon</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TaskFinish,200,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AnchorPoint</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>home_post_sample_table</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>home01_emon_post</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>home01_duran_pre</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>home01_duran</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AnchorPoint</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>home_pre_herb_shed</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>pre</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>home01_duran_pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>home01_duran_post</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>home01_duran</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TaskFinish,200,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AnchorPoint</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>home_post_herb_shed</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>home01_duran_post</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>home01_evan_pre</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>home01_evan</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AnchorPoint</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>home_pre_survivor_fire</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>pre</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>home01_evan_pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>home01_evan_post</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>home01_evan</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TaskFinish,200,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AnchorPoint</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>home_post_sample_table</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>home01_evan_post</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>home01_hearn_pre</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>home01_hearn</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AnchorPoint</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>home_pre_east_watch</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>pre</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>home01_hearn_pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>home01_hearn_post</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>home01_hearn</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TaskFinish,200,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AnchorPoint</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>home_post_watch</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>home01_hearn_post</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>home01_vera_pre</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>home01_vera</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AnchorPoint</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>home_pre_injured_shelter</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>pre</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>home01_vera_pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>home01_vera_post</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>home01_vera</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TaskFinish,200,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>AnchorPoint</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>home_post_vera_room</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>home01_vera_post</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1081,6 +1696,11 @@
           <t>routine_profile_id</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>npc_cfg_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1108,6 +1728,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1135,6 +1760,11 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1162,6 +1792,11 @@
           <t>routine profile id</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NPC unit_npc cfg id</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -1182,6 +1817,114 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>home01_vera</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Home_01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>home01_emon</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>homestead_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Home_01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>home01_duran</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>homestead_merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Home_01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>home_evan</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>home01_evan</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>home_evan</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Home_01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>homestead_01</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>home_hearn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>home01_hearn</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>home_hearn</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1387,6 +2130,206 @@
         <v>20</v>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>home01_emon_pre</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>home01_emon_post</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>home01_duran_pre</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>home01_duran_post</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>home01_evan_pre</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>home01_evan_post</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>home01_hearn_pre</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>home01_hearn_post</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>home01_vera_pre</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>home01_vera_post</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
